--- a/chap14_8/refs/1. 벤포벨/4. 경쟁사 광고비/비타민 경쟁사 광고비.xlsx
+++ b/chap14_8/refs/1. 벤포벨/4. 경쟁사 광고비/비타민 경쟁사 광고비.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\PM2팀\06. 종근당 벤포벨\★★2025 운영\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GPT_AGENT_2025_BOOK\chap14_8\refs\1. 벤포벨\4. 경쟁사 광고비\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47BAD99-ED57-4089-8226-CB11FAC542FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ABA47B-E401-4AA8-83A2-D300876ACBFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -200,7 +191,7 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>계</t>
+    <t>총계</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -898,50 +889,50 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="10" xfId="42" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="11" xfId="42" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="11" xfId="42" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="13" xfId="42" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="13" xfId="42" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="10" xfId="42" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="11" xfId="42" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="11" xfId="42" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="13" xfId="42" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="13" xfId="42" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1300,24 +1291,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:J20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1875" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="13.6875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:10" ht="24.75" x14ac:dyDescent="0.6">
+      <c r="A2" s="17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="J3" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -1349,8 +1340,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A5" s="18" t="s">
         <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1377,13 +1368,13 @@
       <c r="I5" s="3">
         <v>0</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="7">
         <f>SUM(C5:I5)</f>
         <v>439106</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="7"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A6" s="18"/>
       <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1408,13 +1399,13 @@
       <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <f t="shared" ref="J6:J20" si="0">SUM(C6:I6)</f>
         <v>382003</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="7"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A7" s="18"/>
       <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
@@ -1439,77 +1430,77 @@
       <c r="I7" s="3">
         <v>0</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <f t="shared" si="0"/>
         <v>5633167</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A8" s="19"/>
+      <c r="B8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15">
+      <c r="C8" s="12">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
         <v>994393</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="12">
         <v>1074903</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="12">
         <v>413231</v>
       </c>
-      <c r="I8" s="15">
-        <v>0</v>
-      </c>
-      <c r="J8" s="16">
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
         <f t="shared" si="0"/>
         <v>2482527</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="19">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0</v>
-      </c>
-      <c r="E9" s="19">
-        <v>0</v>
-      </c>
-      <c r="F9" s="19">
-        <v>0</v>
-      </c>
-      <c r="G9" s="19">
-        <v>0</v>
-      </c>
-      <c r="H9" s="19">
+      <c r="C9" s="15">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0</v>
+      </c>
+      <c r="H9" s="15">
         <v>58745</v>
       </c>
-      <c r="I9" s="19">
-        <v>0</v>
-      </c>
-      <c r="J9" s="20">
+      <c r="I9" s="15">
+        <v>0</v>
+      </c>
+      <c r="J9" s="16">
         <f t="shared" si="0"/>
         <v>58745</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="7"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A10" s="18"/>
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
@@ -1534,13 +1525,13 @@
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="7">
         <f t="shared" si="0"/>
         <v>482820</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="7"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A11" s="18"/>
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1565,77 +1556,77 @@
       <c r="I11" s="3">
         <v>0</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="7">
         <f t="shared" si="0"/>
         <v>1790911</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14" t="s">
+    <row r="12" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A12" s="19"/>
+      <c r="B12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="15">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15">
-        <v>0</v>
-      </c>
-      <c r="E12" s="15">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15">
-        <v>0</v>
-      </c>
-      <c r="H12" s="15">
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
         <v>742145</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="12">
         <v>68357</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="13">
         <f t="shared" si="0"/>
         <v>810502</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="18" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="17" t="s">
+    <row r="13" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="19">
-        <v>0</v>
-      </c>
-      <c r="D13" s="19">
+      <c r="C13" s="15">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15">
         <v>10104</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="15">
         <v>21405</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="15">
         <v>40433</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="15">
         <v>73174</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="15">
         <v>109505</v>
       </c>
-      <c r="I13" s="19">
-        <v>0</v>
-      </c>
-      <c r="J13" s="20">
+      <c r="I13" s="15">
+        <v>0</v>
+      </c>
+      <c r="J13" s="16">
         <f t="shared" si="0"/>
         <v>254621</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A14" s="7"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A14" s="18"/>
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
@@ -1660,13 +1651,13 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="7">
         <f t="shared" si="0"/>
         <v>3424058</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" s="7"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A15" s="18"/>
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1691,77 +1682,77 @@
       <c r="I15" s="3">
         <v>0</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="7">
         <f t="shared" si="0"/>
         <v>9544546</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14" t="s">
+    <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A16" s="19"/>
+      <c r="B16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>0</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="12">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12">
         <v>846864</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="12">
         <v>1162972</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="12">
         <v>1686226</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="12">
         <v>1358743</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="12">
         <v>1403174</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="12">
         <v>69533</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="13">
         <f t="shared" si="0"/>
         <v>6527512</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="18" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="11">
-        <v>0</v>
-      </c>
-      <c r="D17" s="11">
-        <v>0</v>
-      </c>
-      <c r="E17" s="11">
-        <v>0</v>
-      </c>
-      <c r="F17" s="11">
-        <v>0</v>
-      </c>
-      <c r="G17" s="11">
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
         <v>22289</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="9">
         <v>19599</v>
       </c>
-      <c r="I17" s="11">
-        <v>0</v>
-      </c>
-      <c r="J17" s="12">
+      <c r="I17" s="9">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="0"/>
         <v>41888</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="7"/>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A18" s="18"/>
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
@@ -1786,13 +1777,13 @@
       <c r="I18" s="3">
         <v>740076</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="7">
         <f t="shared" si="0"/>
         <v>1890992</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" s="7"/>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A19" s="18"/>
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
@@ -1817,13 +1808,13 @@
       <c r="I19" s="3">
         <v>758883</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="7">
         <f t="shared" si="0"/>
         <v>3924285</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="7"/>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A20" s="18"/>
       <c r="B20" s="2" t="s">
         <v>23</v>
       </c>
@@ -1848,7 +1839,7 @@
       <c r="I20" s="3">
         <v>533005</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="7">
         <f t="shared" si="0"/>
         <v>1525436</v>
       </c>
@@ -1869,9 +1860,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="16.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="16.6875" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1885,7 +1876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1929,7 +1920,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -1973,7 +1964,7 @@
         <v>9544546</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -2017,7 +2008,7 @@
         <v>6527512</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -2061,7 +2052,7 @@
         <v>3424058</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -2105,7 +2096,7 @@
         <v>254621</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -2149,7 +2140,7 @@
         <v>3924285</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -2193,7 +2184,7 @@
         <v>1525436</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -2237,7 +2228,7 @@
         <v>1890992</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2281,7 +2272,7 @@
         <v>41888</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -2325,7 +2316,7 @@
         <v>5633167</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -2369,7 +2360,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -2413,7 +2404,7 @@
         <v>2482527</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -2457,7 +2448,7 @@
         <v>382003</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -2501,7 +2492,7 @@
         <v>439106</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -2545,7 +2536,7 @@
         <v>319019</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -2589,7 +2580,7 @@
         <v>55800</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -2633,7 +2624,7 @@
         <v>1790911</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -2677,7 +2668,7 @@
         <v>482820</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -2721,7 +2712,7 @@
         <v>810502</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
@@ -2765,7 +2756,7 @@
         <v>58745</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
@@ -2809,7 +2800,7 @@
         <v>20892909</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
@@ -2853,7 +2844,7 @@
         <v>482820</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -2897,7 +2888,7 @@
         <v>319019</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -2941,7 +2932,7 @@
         <v>60300</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -2985,7 +2976,7 @@
         <v>11345977</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -3029,7 +3020,7 @@
         <v>5697053</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -3073,7 +3064,7 @@
         <v>794360</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
